--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H3">
         <v>426</v>
